--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488133_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488133_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6285</v>
+        <v>12.0947</v>
       </c>
       <c r="E2" t="n">
-        <v>12.3973</v>
+        <v>12.6911</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7688</v>
+        <v>-0.5964</v>
       </c>
       <c r="G2" t="n">
         <v>12.3141</v>
@@ -610,13 +610,13 @@
         <v>1.4823</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5738</v>
+        <v>-1.1077</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9302</v>
+        <v>-0.6364</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6437</v>
+        <v>-0.4713</v>
       </c>
       <c r="V2" t="n">
         <v>1.2589</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.3231</v>
+        <v>8.2738</v>
       </c>
       <c r="E3" t="n">
         <v>5.6634</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6596</v>
+        <v>2.6104</v>
       </c>
       <c r="G3" t="n">
         <v>5.9977</v>
@@ -688,13 +688,13 @@
         <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8038</v>
+        <v>-0.8531</v>
       </c>
       <c r="T3" t="n">
         <v>-0.4414</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3624</v>
+        <v>-0.4116</v>
       </c>
       <c r="V3" t="n">
         <v>2.2027</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7338</v>
+        <v>3.0215</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0918</v>
+        <v>0.7981</v>
       </c>
       <c r="F4" t="n">
-        <v>2.642</v>
+        <v>2.2234</v>
       </c>
       <c r="G4" t="n">
         <v>2.1603</v>
@@ -766,13 +766,13 @@
         <v>1.6676</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4994</v>
+        <v>-0.213</v>
       </c>
       <c r="T4" t="n">
-        <v>0.051</v>
+        <v>-0.2428</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4484</v>
+        <v>0.0298</v>
       </c>
       <c r="V4" t="n">
         <v>1.2594</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5227</v>
+        <v>2.3761</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0087</v>
+        <v>1.8129</v>
       </c>
       <c r="F5" t="n">
-        <v>0.514</v>
+        <v>0.5632</v>
       </c>
       <c r="G5" t="n">
         <v>0.4161</v>
@@ -844,13 +844,13 @@
         <v>1.297</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4683</v>
+        <v>-0.6149</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0037</v>
+        <v>-0.1996</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4646</v>
+        <v>-0.4154</v>
       </c>
       <c r="V5" t="n">
         <v>2.2044</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.584</v>
+        <v>2.0501</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2107</v>
+        <v>2.5044</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6266</v>
+        <v>-0.4543</v>
       </c>
       <c r="G6" t="n">
         <v>1.1761</v>
@@ -922,13 +922,13 @@
         <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-0.4971</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4377</v>
+        <v>-0.1439</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5255</v>
+        <v>-0.3532</v>
       </c>
       <c r="V6" t="n">
         <v>0.63</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3883</v>
+        <v>0.0956</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.4097</v>
+        <v>-1.8993</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7979</v>
+        <v>1.9949</v>
       </c>
       <c r="G7" t="n">
         <v>-2.9715</v>
@@ -1000,13 +1000,13 @@
         <v>2.0382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2517</v>
+        <v>-0.5444</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3756</v>
+        <v>-0.1141</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6273</v>
+        <v>-0.4303</v>
       </c>
       <c r="V7" t="n">
         <v>1.5733</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1777</v>
+        <v>-2.0059</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9847</v>
+        <v>-0.8868</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.193</v>
+        <v>-1.1192</v>
       </c>
       <c r="G10" t="n">
         <v>-0.599</v>
@@ -1234,13 +1234,13 @@
         <v>0.3706</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.376</v>
+        <v>-0.2043</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4377</v>
+        <v>-0.3398</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0617</v>
+        <v>0.1355</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5733</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7944</v>
+        <v>-2.8682</v>
       </c>
       <c r="E11" t="n">
         <v>-1.0864</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.708</v>
+        <v>-1.7818</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0184</v>
@@ -1312,13 +1312,13 @@
         <v>0.3706</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2768</v>
+        <v>-0.3507</v>
       </c>
       <c r="T11" t="n">
         <v>-0.383</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1062</v>
+        <v>0.0323</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9433</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6363</v>
+        <v>-5.4657</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.923</v>
+        <v>-4.6292</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7133</v>
+        <v>-0.8364</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7966</v>
@@ -1390,13 +1390,13 @@
         <v>2.4087</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2659</v>
+        <v>-1.0953</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7113</v>
+        <v>-0.4175</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5546</v>
+        <v>-0.6778</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2033</v>
@@ -1426,7 +1426,7 @@
         <v>15.5908</v>
       </c>
       <c r="E13" t="n">
-        <v>14.0181</v>
+        <v>14.0182</v>
       </c>
       <c r="F13" t="n">
         <v>1.572499999999999</v>
@@ -1468,13 +1468,13 @@
         <v>14.823</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.9812</v>
+        <v>-5.9816</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.0278</v>
+        <v>-3.0279</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.9535</v>
+        <v>-2.9537</v>
       </c>
       <c r="V13" t="n">
         <v>3.7794</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. ROPERO BENIEZ</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0603</v>
+        <v>2.8499</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6375</v>
+        <v>4.7961</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5772</v>
+        <v>-1.9462</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9967</v>
+        <v>0.8035</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8216</v>
+        <v>0.4167</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8249</v>
+        <v>0.3868</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8652</v>
+        <v>4.4459</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1388</v>
+        <v>1.8935</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7264</v>
+        <v>2.5524</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.8685</v>
+        <v>-3.6424</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3173</v>
+        <v>-1.4768</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.5513</v>
+        <v>-2.1656</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1117</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1499</v>
+        <v>-0.3706</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0382</v>
+        <v>0.9264</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8609</v>
+        <v>0.8611</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6077</v>
+        <v>0.0914</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2532</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3144</v>
+        <v>0.6294</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3144</v>
+        <v>0.6294</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5578</v>
+        <v>1.8814</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2086</v>
+        <v>1.3373</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6508</v>
+        <v>0.544</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8035</v>
+        <v>-1.2841</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4167</v>
+        <v>-1.9017</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3868</v>
+        <v>0.6175</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4459</v>
+        <v>1.7058</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8935</v>
+        <v>-0.3784</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5524</v>
+        <v>2.0842</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.6424</v>
+        <v>-2.99</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4768</v>
+        <v>-1.5233</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1656</v>
+        <v>-1.4667</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.3706</v>
+        <v>-1.297</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9264</v>
+        <v>1.6676</v>
       </c>
       <c r="S15" t="n">
-        <v>0.569</v>
+        <v>1.5361</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4961</v>
+        <v>0.6146</v>
       </c>
       <c r="U15" t="n">
-        <v>1.0652</v>
+        <v>0.9214</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6294</v>
+        <v>1.2589</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6294</v>
+        <v>0.3139</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>J. ROPERO BENIEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7846</v>
+        <v>1.8359</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0436</v>
+        <v>2.4623</v>
       </c>
       <c r="F16" t="n">
-        <v>0.741</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2841</v>
+        <v>0.9967</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9017</v>
+        <v>1.8216</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6175</v>
+        <v>-0.8249</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7058</v>
+        <v>3.8652</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3784</v>
+        <v>3.1388</v>
       </c>
       <c r="L16" t="n">
-        <v>2.0842</v>
+        <v>0.7264</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.99</v>
+        <v>-2.8685</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5233</v>
+        <v>-1.3173</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.4667</v>
+        <v>-1.5513</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3706</v>
+        <v>-1.1117</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.297</v>
+        <v>-3.1499</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6676</v>
+        <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4393</v>
+        <v>1.6365</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3209</v>
+        <v>1.4326</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1184</v>
+        <v>0.2039</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="W16" t="n">
-        <v>0.3139</v>
+        <v>0.3144</v>
       </c>
       <c r="X16" t="n">
-        <v>0.945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MORALES ZARCO</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1947</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5413</v>
+        <v>-0.6446</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3465</v>
+        <v>-0.2178</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.0858</v>
+        <v>-0.9582000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4654</v>
+        <v>-0.7155</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6204</v>
+        <v>-0.2427</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0702</v>
+        <v>-0.5899</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1946</v>
+        <v>-0.6314</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1244</v>
+        <v>0.0415</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0157</v>
+        <v>-0.3683</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2708</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7448</v>
+        <v>-0.2841</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.1499</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3565</v>
+        <v>0.0958</v>
       </c>
       <c r="T17" t="n">
-        <v>1.736</v>
+        <v>-0.0547</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.1505</v>
       </c>
       <c r="V17" t="n">
-        <v>1.5727</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.9428</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>J. MORALES ZARCO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7886</v>
+        <v>-1.1992</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6446</v>
+        <v>-1.4226</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.144</v>
+        <v>0.2234</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-2.0858</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7155</v>
+        <v>-1.4654</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2427</v>
+        <v>-0.6204</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5899</v>
+        <v>-0.0702</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6314</v>
+        <v>-0.1946</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0415</v>
+        <v>0.1244</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3683</v>
+        <v>-2.0157</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-1.2708</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2841</v>
+        <v>-0.7448</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.1499</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1696</v>
+        <v>1.352</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0547</v>
+        <v>0.8546</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2243</v>
+        <v>0.4974</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.5727</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.9428</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8574</v>
+        <v>-1.2944</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7173</v>
+        <v>-1.1297</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1401</v>
+        <v>-0.1647</v>
       </c>
       <c r="G19" t="n">
         <v>-2.081</v>
@@ -1936,13 +1936,13 @@
         <v>1.4823</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3323</v>
+        <v>0.2307</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3283</v>
+        <v>0.2593</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.004</v>
+        <v>-0.0286</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6782</v>
+        <v>-2.531</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2986</v>
+        <v>-1.2007</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3796</v>
+        <v>-1.3303</v>
       </c>
       <c r="G20" t="n">
         <v>-1.859</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2072</v>
+        <v>-0.06</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1094</v>
+        <v>-0.0115</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V20" t="n">
         <v>0.3144</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>P. LOPEZ MACIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7474</v>
+        <v>-3.3721</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8718</v>
+        <v>-2.2528</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8756</v>
+        <v>-1.1193</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4851</v>
+        <v>-2.5621</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3023</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1827</v>
+        <v>-1.9446</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5881</v>
+        <v>-0.7377</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4636</v>
+        <v>0.4851</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1244</v>
+        <v>-1.2228</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0731</v>
+        <v>-1.8244</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.766</v>
+        <v>-1.1026</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3071</v>
+        <v>-0.7219</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4087</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.297</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2236</v>
+        <v>-0.4209</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.383</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1594</v>
+        <v>0.1492</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.63</v>
+        <v>-0.945</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6289</v>
+        <v>-0.945</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. LOPEZ MACIAS</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.8142</v>
+        <v>-3.429</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4486</v>
+        <v>-2.578</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3655</v>
+        <v>-0.8509</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5621</v>
+        <v>-0.4851</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.3023</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9446</v>
+        <v>-0.1827</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7377</v>
+        <v>0.5881</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4851</v>
+        <v>0.4636</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2228</v>
+        <v>0.1244</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8244</v>
+        <v>-1.0731</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1026</v>
+        <v>-0.766</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7219</v>
+        <v>-0.3071</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.297</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.863</v>
+        <v>0.0948</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.766</v>
+        <v>-0.0892</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.097</v>
+        <v>0.184</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.945</v>
+        <v>-0.63</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.945</v>
+        <v>0.6289</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.171</v>
+        <v>-4.3904</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0823</v>
+        <v>-0.474</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.0888</v>
+        <v>-3.9164</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6707</v>
@@ -2248,13 +2248,13 @@
         <v>1.8529</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4059</v>
+        <v>0.1865</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5397</v>
+        <v>0.148</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1338</v>
+        <v>0.0385</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8327</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.7419</v>
+        <v>-5.0794</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8577</v>
+        <v>-0.466</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.8843</v>
+        <v>-4.6134</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8278</v>
@@ -2326,13 +2326,13 @@
         <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1937</v>
+        <v>0.4688</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1131</v>
+        <v>0.2786</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0806</v>
+        <v>0.1903</v>
       </c>
       <c r="V24" t="n">
         <v>-3.4616</v>
@@ -2362,25 +2362,25 @@
         <v>-15.5907</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.572499999999999</v>
+        <v>-1.572699999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-14.0184</v>
+        <v>-14.0181</v>
       </c>
       <c r="G25" t="n">
         <v>-15.0136</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.602</v>
+        <v>-7.601999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-7.4114</v>
       </c>
       <c r="J25" t="n">
-        <v>6.839599999999999</v>
+        <v>6.839600000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>4.076199999999999</v>
+        <v>4.0762</v>
       </c>
       <c r="L25" t="n">
         <v>2.7635</v>
@@ -2407,16 +2407,16 @@
         <v>5.9814</v>
       </c>
       <c r="T25" t="n">
-        <v>2.9537</v>
+        <v>2.953600000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>3.0279</v>
+        <v>3.0278</v>
       </c>
       <c r="V25" t="n">
         <v>-3.7795</v>
       </c>
       <c r="W25" t="n">
-        <v>3.4571</v>
+        <v>3.457100000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-7.236499999999999</v>
